--- a/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27004"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="11_C0200DA9FB882CF1ABF1BE001C5B9906202A95AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8ECCDAD-DF4E-4414-8F2C-09422E1BC531}"/>
+  <xr:revisionPtr revIDLastSave="391" documentId="11_C0200DA9FB882CF1ABF1BE001C5B9906202A95AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF27E093-F63D-4AC8-9F2D-AD6FF8C42E0E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId1"/>
-    <sheet name="Projects" sheetId="1" r:id="rId2"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId3"/>
+    <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
+    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="112">
   <si>
     <t>Project ID</t>
   </si>
@@ -77,6 +78,24 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>SEH Taxonomy</t>
+  </si>
+  <si>
+    <t>RISE Taxonomy</t>
+  </si>
+  <si>
+    <t>Flagship</t>
+  </si>
+  <si>
+    <t>Indirect Category</t>
+  </si>
+  <si>
+    <t>Indirect Taxonomy</t>
   </si>
   <si>
     <t>Nature, Climate, Energy, and Resilience Programme</t>
@@ -490,7 +509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -567,6 +586,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -575,7 +673,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -668,6 +766,83 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -973,6 +1148,374 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74260D8F-AF74-46D9-8F43-C6873EC3DB38}">
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="39.7109375" customWidth="1"/>
+    <col min="15" max="19" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="45.75">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="20" customFormat="1" ht="121.5">
+      <c r="A2" s="48">
+        <v>143659</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="46">
+        <v>64339</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="24"/>
+      <c r="H2" s="32">
+        <v>5600000</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="54"/>
+      <c r="L2" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="57"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+    </row>
+    <row r="3" spans="1:19" ht="60.75">
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="27">
+        <v>0</v>
+      </c>
+      <c r="H3" s="27">
+        <v>1500</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="47"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+    </row>
+    <row r="4" spans="1:19" ht="76.5">
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="27">
+        <v>0</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="47"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+    </row>
+    <row r="5" spans="1:19" ht="229.5">
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="27">
+        <v>0</v>
+      </c>
+      <c r="H5" s="27">
+        <v>3000</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="47"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+    </row>
+    <row r="6" spans="1:19" ht="137.25">
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="27">
+        <v>0</v>
+      </c>
+      <c r="H6" s="27">
+        <v>100</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="47"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+    </row>
+    <row r="7" spans="1:19" ht="336">
+      <c r="A7" s="63">
+        <v>5574</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="60">
+        <v>2170030</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="28">
+        <v>3</v>
+      </c>
+      <c r="H7" s="29">
+        <v>6</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="55"/>
+      <c r="L7" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="57"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+    </row>
+    <row r="8" spans="1:19" ht="121.5">
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27">
+        <v>200</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="69"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+    </row>
+    <row r="9" spans="1:19" ht="167.25">
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0</v>
+      </c>
+      <c r="H9" s="27">
+        <v>500</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="67"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="M10" s="31"/>
+    </row>
+    <row r="11" spans="1:19"/>
+    <row r="12" spans="1:19">
+      <c r="A12" s="9"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{A1F9346D-0655-49D7-9674-07A8FD12E742}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E06CD4F-A140-452E-B647-06E438A268E7}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E11</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A083FA-61BB-468B-9E7C-D191D0F0C820}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
@@ -1031,33 +1574,33 @@
         <v>143659</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" s="34">
         <v>64339</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G2" s="24"/>
       <c r="H2" s="32">
         <v>5600000</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K2" s="24"/>
       <c r="L2" s="34" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M2" s="33"/>
     </row>
@@ -1067,10 +1610,10 @@
       <c r="C3" s="36"/>
       <c r="D3" s="34"/>
       <c r="E3" s="27" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G3" s="27">
         <v>0</v>
@@ -1079,7 +1622,7 @@
         <v>1500</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J3" s="34"/>
       <c r="K3" s="26"/>
@@ -1092,19 +1635,19 @@
       <c r="C4" s="36"/>
       <c r="D4" s="34"/>
       <c r="E4" s="27" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G4" s="27">
         <v>0</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J4" s="34"/>
       <c r="K4" s="26"/>
@@ -1117,10 +1660,10 @@
       <c r="C5" s="36"/>
       <c r="D5" s="34"/>
       <c r="E5" s="27" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G5" s="27">
         <v>0</v>
@@ -1129,7 +1672,7 @@
         <v>3000</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J5" s="34"/>
       <c r="K5" s="26"/>
@@ -1142,10 +1685,10 @@
       <c r="C6" s="36"/>
       <c r="D6" s="34"/>
       <c r="E6" s="28" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G6" s="27">
         <v>0</v>
@@ -1154,7 +1697,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J6" s="34"/>
       <c r="K6" s="26"/>
@@ -1166,19 +1709,19 @@
         <v>5574</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" s="35">
         <v>2170030</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G7" s="28">
         <v>3</v>
@@ -1187,14 +1730,14 @@
         <v>6</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K7" s="26"/>
       <c r="L7" s="35" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M7" s="33"/>
     </row>
@@ -1204,17 +1747,17 @@
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
       <c r="E8" s="27" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G8" s="27"/>
       <c r="H8" s="27">
         <v>200</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J8" s="35"/>
       <c r="K8" s="26"/>
@@ -1227,10 +1770,10 @@
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
       <c r="E9" s="27" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G9" s="27">
         <v>0</v>
@@ -1239,7 +1782,7 @@
         <v>500</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J9" s="35"/>
       <c r="K9" s="26"/>
@@ -1287,7 +1830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
@@ -1329,10 +1872,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>9</v>
@@ -1343,19 +1886,19 @@
         <v>143659</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4">
         <v>64339</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G2" s="6">
         <v>11</v>
@@ -1364,16 +1907,16 @@
         <v>28</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="57.95">
@@ -1382,10 +1925,10 @@
       <c r="C3" s="5"/>
       <c r="D3" s="4"/>
       <c r="E3" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
@@ -1394,16 +1937,16 @@
         <v>4</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="57.95">
@@ -1412,10 +1955,10 @@
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -1424,16 +1967,16 @@
         <v>3</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J4" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" t="s">
         <v>56</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="101.45">
@@ -1442,10 +1985,10 @@
       <c r="C5" s="5"/>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -1454,16 +1997,16 @@
         <v>3</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="130.5">
@@ -1472,10 +2015,10 @@
       <c r="C6" s="5"/>
       <c r="D6" s="4"/>
       <c r="E6" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
@@ -1484,16 +2027,16 @@
         <v>30</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J6" s="15">
         <v>500</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.45">
@@ -1514,69 +2057,69 @@
         <v>5574</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4">
         <v>2170030</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="72.599999999999994">
       <c r="E9" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="130.5">
       <c r="E10" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
@@ -1585,23 +2128,23 @@
         <v>50</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.45"/>
     <row r="12" spans="1:12" ht="14.45"/>
     <row r="13" spans="1:12" ht="14.45">
       <c r="A13" s="9" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1624,7 +2167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
@@ -1634,160 +2177,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="37" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="37"/>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="37"/>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="38" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="38"/>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="38"/>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="38"/>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="38"/>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="39" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="39"/>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="40" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="40"/>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="40"/>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1802,6 +2345,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2050,28 +2613,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E895C624-286E-404E-ABC2-61E1D4CF12D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4264E7FE-F362-4EE6-893A-3F86363FF155}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2079,5 +2622,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4264E7FE-F362-4EE6-893A-3F86363FF155}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E895C624-286E-404E-ABC2-61E1D4CF12D6}"/>
 </file>
--- a/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="462" documentId="11_C0200DA9FB882CF1ABF1BE001C5B9906202A95AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C406E6E6-E5EC-47CB-B208-51D40FCB8663}"/>
+  <xr:revisionPtr revIDLastSave="468" documentId="11_C0200DA9FB882CF1ABF1BE001C5B9906202A95AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFB10E79-18EA-4D5D-A5AC-A0058DB76054}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,7 +116,7 @@
     <t>Number of health centers benefiting from UNDP solar PV installation</t>
   </si>
   <si>
-    <t>Each health centre is serving a catchment population of about 200,000 people. Estimated 5,600,00 people will be served by the health facilities 
+    <t>Each health centre is serving a catchment population of about 200,000 people. Estimated 5,600,000 people will be served by the health facilities 
 UNDP support solar PV installation in 11 health centers. Additional 17 health centres will be supported.  In addition, UNDP has supported solar PV installationsd in 8 schools, 7 border immigration offices and 5 markets across the Country</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t>8 Selected public schools will benefit from solar PV installations. Total estimated school popultation is 1500 pupils</t>
   </si>
   <si>
-    <t>Small Enterprises</t>
+    <t>Electricity Access</t>
   </si>
   <si>
     <t>Number of small enterprises working in the markets where solar has been installed</t>
@@ -197,9 +197,6 @@
   </si>
   <si>
     <t>Regional</t>
-  </si>
-  <si>
-    <t>Electricity Access</t>
   </si>
   <si>
     <t>Additional electricty generation capacity added</t>
@@ -417,6 +414,9 @@
   </si>
   <si>
     <t>Support for the development of medium enterprises in the energy transition market</t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
   </si>
   <si>
     <t>Support for the development of small enterprises in the energy transition market</t>
@@ -529,7 +529,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,6 +557,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,7 +731,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -887,6 +893,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1305,7 +1312,7 @@
       </c>
       <c r="G2" s="24"/>
       <c r="H2" s="55">
-        <v>7300000</v>
+        <v>5600000</v>
       </c>
       <c r="I2" s="41" t="s">
         <v>25</v>
@@ -1344,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="53">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="I3" s="41" t="s">
         <v>31</v>
@@ -1373,7 +1380,7 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="45"/>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="67" t="s">
         <v>32</v>
       </c>
       <c r="F4" s="40" t="s">
@@ -1544,17 +1551,17 @@
       <c r="C8" s="43"/>
       <c r="D8" s="45"/>
       <c r="E8" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="47" t="s">
         <v>51</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>52</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="24">
         <v>200</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="49"/>
       <c r="K8" s="42"/>
@@ -1582,7 +1589,7 @@
         <v>38</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9" s="24">
         <v>0</v>
@@ -1591,7 +1598,7 @@
         <v>500</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="52"/>
       <c r="K9" s="42"/>
@@ -1720,10 +1727,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>56</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="18" customFormat="1" ht="121.5">
@@ -1750,7 +1757,7 @@
         <v>5600000</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J2" s="64" t="s">
         <v>26</v>
@@ -1779,7 +1786,7 @@
         <v>1500</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J3" s="64"/>
       <c r="K3" s="24"/>
@@ -1801,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>60</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="J4" s="64"/>
       <c r="K4" s="24"/>
@@ -1817,10 +1824,10 @@
       <c r="C5" s="66"/>
       <c r="D5" s="64"/>
       <c r="E5" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="26" t="s">
         <v>62</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>63</v>
       </c>
       <c r="G5" s="25">
         <v>0</v>
@@ -1829,7 +1836,7 @@
         <v>3000</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J5" s="64"/>
       <c r="K5" s="24"/>
@@ -1842,7 +1849,7 @@
       <c r="C6" s="66"/>
       <c r="D6" s="64"/>
       <c r="E6" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="26" t="s">
         <v>39</v>
@@ -1904,17 +1911,17 @@
       <c r="C8" s="65"/>
       <c r="D8" s="65"/>
       <c r="E8" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="27" t="s">
         <v>51</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>52</v>
       </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25">
         <v>200</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="24"/>
@@ -1927,10 +1934,10 @@
       <c r="C9" s="65"/>
       <c r="D9" s="65"/>
       <c r="E9" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9" s="25">
         <v>0</v>
@@ -1939,7 +1946,7 @@
         <v>500</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J9" s="65"/>
       <c r="K9" s="24"/>
@@ -2029,10 +2036,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="L1" s="17" t="s">
         <v>9</v>
@@ -2064,16 +2071,16 @@
         <v>28</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" t="s">
         <v>70</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="57.95">
@@ -2085,7 +2092,7 @@
         <v>29</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -2094,16 +2101,16 @@
         <v>4</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="K3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K3" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="L3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="57.95">
@@ -2115,7 +2122,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -2124,16 +2131,16 @@
         <v>3</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="101.45">
@@ -2142,10 +2149,10 @@
       <c r="C5" s="3"/>
       <c r="D5" s="2"/>
       <c r="E5" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
@@ -2154,16 +2161,16 @@
         <v>3</v>
       </c>
       <c r="I5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="K5" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="10" t="s">
-        <v>81</v>
-      </c>
       <c r="L5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="130.5">
@@ -2172,7 +2179,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="2"/>
       <c r="E6" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>39</v>
@@ -2184,16 +2191,16 @@
         <v>30</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J6" s="13">
         <v>500</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.45">
@@ -2226,57 +2233,57 @@
         <v>19</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="J8" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" t="s">
         <v>89</v>
-      </c>
-      <c r="L8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="72.599999999999994">
       <c r="E9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="130.5">
       <c r="E10" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
@@ -2285,23 +2292,23 @@
         <v>50</v>
       </c>
       <c r="I10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="J10" s="14" t="s">
-        <v>97</v>
-      </c>
       <c r="K10" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.45"/>
     <row r="12" spans="1:12" ht="14.45"/>
     <row r="13" spans="1:12" ht="14.45">
       <c r="A13" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2341,127 +2348,127 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="67" t="s">
-        <v>51</v>
+      <c r="A2" s="68" t="s">
+        <v>32</v>
       </c>
       <c r="B2" s="57" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="57" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="67" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="57" t="s">
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="57" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="57" t="s">
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="68" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="67" t="s">
+      <c r="B5" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="57" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="68" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="67" t="s">
+      <c r="B6" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="57" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="57" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="57" t="s">
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="68" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="67" t="s">
+      <c r="B8" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="57" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="57" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="57" t="s">
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="68" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="67" t="s">
+      <c r="B10" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="68" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="68" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="67" t="s">
+      <c r="B11" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="68" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="68" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="67" t="s">
+      <c r="B12" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="57" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="68" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="67" t="s">
+      <c r="B13" s="69" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="68" t="s">
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="68" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="67" t="s">
+      <c r="B14" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="68" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="68" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="67" t="s">
+      <c r="B15" s="69" t="s">
         <v>120</v>
       </c>
-      <c r="B15" s="68" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="68" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="69" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="68" t="s">
         <v>38</v>
       </c>
       <c r="B17" s="57" t="s">
@@ -2469,42 +2476,42 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="68" t="s">
+      <c r="A18" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="69" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="69" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="69" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="67" t="s">
+      <c r="A21" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="70" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="69" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2514,8 +2521,70 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Gloria Namande</DisplayName>
+        <AccountId>1432</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Tom Sengalama</DisplayName>
+        <AccountId>1974</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Michael Kiza</DisplayName>
+        <AccountId>1710</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Elsie Attafuah</DisplayName>
+        <AccountId>2018</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sheila Ngatia</DisplayName>
+        <AccountId>2019</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2540,6 +2609,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2619,6 +2689,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2762,70 +2837,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Gloria Namande</DisplayName>
-        <AccountId>1432</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Tom Sengalama</DisplayName>
-        <AccountId>1974</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Michael Kiza</DisplayName>
-        <AccountId>1710</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Elsie Attafuah</DisplayName>
-        <AccountId>2018</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sheila Ngatia</DisplayName>
-        <AccountId>2019</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E895C624-286E-404E-ABC2-61E1D4CF12D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4264E7FE-F362-4EE6-893A-3F86363FF155}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2833,5 +2846,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4264E7FE-F362-4EE6-893A-3F86363FF155}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDBC726A-7CEF-4FCE-950C-70EF97981F6A}"/>
 </file>
--- a/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="11_C0200DA9FB882CF1ABF1BE001C5B9906202A95AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFB10E79-18EA-4D5D-A5AC-A0058DB76054}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="11_C0200DA9FB882CF1ABF1BE001C5B9906202A95AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCB855B1-6948-46C5-8F62-F339D45BDF19}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="134">
   <si>
     <t>Project ID</t>
   </si>
@@ -170,7 +170,7 @@
     <t>NAMA Integrated Wastewater Treatment</t>
   </si>
   <si>
-    <t>PIMS+</t>
+    <t>https://co.pims.undp.org/project/view?id=5574</t>
   </si>
   <si>
     <t xml:space="preserve">Number of policy and regulatory proposals developed and adopted </t>
@@ -248,6 +248,9 @@
     <t>Capacity Training</t>
   </si>
   <si>
+    <t>PIMS+</t>
+  </si>
+  <si>
     <t xml:space="preserve">Number of beneficiaries/population </t>
   </si>
   <si>
@@ -447,13 +450,16 @@
   </si>
   <si>
     <t>Any other type of beneficiary (please specify justification in Notes)</t>
+  </si>
+  <si>
+    <t>Building Resilient Communities, Wetland Ecosystems and Associated Catchments in Uganda</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,8 +534,16 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,12 +571,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,19 +673,6 @@
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -702,11 +697,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -718,26 +713,32 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color rgb="FF000000"/>
-      </bottom>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -805,103 +806,128 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1208,14 +1234,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74260D8F-AF74-46D9-8F43-C6873EC3DB38}">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="2" max="3" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="18"/>
+    <col min="5" max="6" width="20.7109375" style="18" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="18" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="18" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="18" customWidth="1"/>
     <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -1226,405 +1254,502 @@
     <col min="19" max="20" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="45.75">
+    <row r="1" spans="1:21" ht="45">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="50" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="58" t="s">
+      <c r="L1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="58" t="s">
+      <c r="N1" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="58" t="s">
+      <c r="O1" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="59" t="s">
+      <c r="P1" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="59" t="s">
+      <c r="Q1" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="60" t="s">
+      <c r="R1" s="44" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="60" t="s">
+      <c r="T1" s="44" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="33" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="18" customFormat="1" ht="183">
+    <row r="2" spans="1:21" s="18" customFormat="1" ht="180">
       <c r="A2" s="35">
         <v>143659</v>
       </c>
       <c r="B2" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="52">
         <v>1980000</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="55">
-        <v>5600000</v>
-      </c>
-      <c r="I2" s="41" t="s">
+      <c r="G2" s="22"/>
+      <c r="H2" s="54">
+        <v>2200000</v>
+      </c>
+      <c r="I2" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="61" t="s">
+      <c r="K2" s="37"/>
+      <c r="L2" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="54"/>
-      <c r="N2" s="62" t="s">
+      <c r="M2" s="39"/>
+      <c r="N2" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="63"/>
-    </row>
-    <row r="3" spans="1:21" ht="60.75">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="39" t="s">
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="47"/>
+    </row>
+    <row r="3" spans="1:21" ht="60">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <v>0</v>
       </c>
-      <c r="H3" s="53">
+      <c r="H3" s="58">
         <v>1500</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="61" t="s">
+      <c r="K3" s="37"/>
+      <c r="L3" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="54"/>
-      <c r="N3" s="62" t="s">
+      <c r="M3" s="39"/>
+      <c r="N3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="63"/>
-    </row>
-    <row r="4" spans="1:21" ht="152.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="67" t="s">
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="47"/>
+    </row>
+    <row r="4" spans="1:21" ht="165">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <v>0</v>
       </c>
-      <c r="H4" s="53">
+      <c r="H4" s="58">
         <v>300000</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="J4" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="61" t="s">
+      <c r="K4" s="37"/>
+      <c r="L4" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="62" t="s">
+      <c r="M4" s="39"/>
+      <c r="N4" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="63"/>
-    </row>
-    <row r="5" spans="1:21" ht="60.75">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="39" t="s">
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="47"/>
+    </row>
+    <row r="5" spans="1:21" ht="75">
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <v>1</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="22">
         <v>300</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="45"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="61" t="s">
+      <c r="J5" s="57"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="54"/>
-      <c r="N5" s="62" t="s">
+      <c r="M5" s="39"/>
+      <c r="N5" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="63"/>
-    </row>
-    <row r="6" spans="1:21" ht="137.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46" t="s">
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="47"/>
+    </row>
+    <row r="6" spans="1:21" ht="150">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <v>0</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="22">
         <v>100</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="45"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="61" t="s">
+      <c r="J6" s="57"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="54"/>
-      <c r="N6" s="62" t="s">
+      <c r="M6" s="39"/>
+      <c r="N6" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="63"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="63"/>
-    </row>
-    <row r="7" spans="1:21" ht="336">
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="47"/>
+    </row>
+    <row r="7" spans="1:21" ht="345">
       <c r="A7" s="35">
         <v>5574</v>
       </c>
       <c r="B7" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="52">
         <v>2170030</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="23">
         <v>3</v>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="61">
         <v>6</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="48" t="s">
+      <c r="J7" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="42"/>
-      <c r="L7" s="61" t="s">
+      <c r="K7" s="37"/>
+      <c r="L7" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="54"/>
-      <c r="N7" s="62" t="s">
+      <c r="M7" s="39"/>
+      <c r="N7" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="54" t="s">
+      <c r="O7" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54" t="s">
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="54" t="s">
+      <c r="R7" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="S7" s="63"/>
-      <c r="T7" s="54" t="s">
+      <c r="S7" s="47"/>
+      <c r="T7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="U7" s="63">
+      <c r="U7" s="47">
         <v>2800000</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="121.5">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="39" t="s">
+    <row r="8" spans="1:21" ht="120">
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24">
+      <c r="G8" s="22"/>
+      <c r="H8" s="22">
         <v>200</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="49"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="61" t="s">
+      <c r="J8" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="37"/>
+      <c r="L8" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="54"/>
-      <c r="N8" s="62" t="s">
+      <c r="M8" s="39"/>
+      <c r="N8" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="63"/>
-    </row>
-    <row r="9" spans="1:21" ht="167.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="39" t="s">
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="47"/>
+    </row>
+    <row r="9" spans="1:21" ht="180">
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="72">
         <v>0</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="72">
         <v>500</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="52"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="61" t="s">
+      <c r="J9" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="74"/>
+      <c r="L9" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="M9" s="54"/>
-      <c r="N9" s="62" t="s">
+      <c r="M9" s="75"/>
+      <c r="N9" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="63"/>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="M10" s="29"/>
-    </row>
-    <row r="11" spans="1:21"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="77"/>
+    </row>
+    <row r="10" spans="1:21" ht="90" customHeight="1">
+      <c r="A10" s="78">
+        <v>5711</v>
+      </c>
+      <c r="B10" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="78"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+    </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="7"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" ht="15" customHeight="1">
+      <c r="A13" s="78"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
+  </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q9" xr:uid="{8187306B-B638-43B4-8CDE-16BB9DF6BF18}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
@@ -1656,6 +1781,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{A1F9346D-0655-49D7-9674-07A8FD12E742}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{F77A35E2-7183-4711-BD26-43CB0CB851CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1733,17 +1859,17 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="18" customFormat="1" ht="121.5">
-      <c r="A2" s="64">
+    <row r="2" spans="1:13" s="18" customFormat="1" ht="120">
+      <c r="A2" s="67">
         <v>143659</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="64">
+      <c r="D2" s="67">
         <v>64339</v>
       </c>
       <c r="E2" s="22" t="s">
@@ -1759,20 +1885,20 @@
       <c r="I2" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="64" t="s">
+      <c r="J2" s="67" t="s">
         <v>26</v>
       </c>
       <c r="K2" s="22"/>
-      <c r="L2" s="64" t="s">
+      <c r="L2" s="67" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="31"/>
     </row>
-    <row r="3" spans="1:13" ht="60.75">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="64"/>
+    <row r="3" spans="1:13" ht="60">
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="67"/>
       <c r="E3" s="25" t="s">
         <v>29</v>
       </c>
@@ -1788,16 +1914,16 @@
       <c r="I3" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="64"/>
+      <c r="J3" s="67"/>
       <c r="K3" s="24"/>
-      <c r="L3" s="64"/>
+      <c r="L3" s="67"/>
       <c r="M3" s="31"/>
     </row>
-    <row r="4" spans="1:13" ht="76.5">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="64"/>
+    <row r="4" spans="1:13" ht="75">
+      <c r="A4" s="67"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="67"/>
       <c r="E4" s="25" t="s">
         <v>35</v>
       </c>
@@ -1813,16 +1939,16 @@
       <c r="I4" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="64"/>
+      <c r="J4" s="67"/>
       <c r="K4" s="24"/>
-      <c r="L4" s="64"/>
+      <c r="L4" s="67"/>
       <c r="M4" s="28"/>
     </row>
-    <row r="5" spans="1:13" ht="229.5">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="64"/>
+    <row r="5" spans="1:13" ht="240">
+      <c r="A5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="67"/>
       <c r="E5" s="25" t="s">
         <v>61</v>
       </c>
@@ -1838,16 +1964,16 @@
       <c r="I5" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="64"/>
+      <c r="J5" s="67"/>
       <c r="K5" s="24"/>
-      <c r="L5" s="64"/>
+      <c r="L5" s="67"/>
       <c r="M5" s="28"/>
     </row>
-    <row r="6" spans="1:13" ht="137.25">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="64"/>
+    <row r="6" spans="1:13" ht="150">
+      <c r="A6" s="67"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="67"/>
       <c r="E6" s="26" t="s">
         <v>64</v>
       </c>
@@ -1863,22 +1989,22 @@
       <c r="I6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="64"/>
+      <c r="J6" s="67"/>
       <c r="K6" s="24"/>
-      <c r="L6" s="64"/>
+      <c r="L6" s="67"/>
       <c r="M6" s="28"/>
     </row>
-    <row r="7" spans="1:13" ht="336">
-      <c r="A7" s="65">
+    <row r="7" spans="1:13" ht="345">
+      <c r="A7" s="68">
         <v>5574</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="65">
+      <c r="C7" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="68">
         <v>2170030</v>
       </c>
       <c r="E7" s="26" t="s">
@@ -1896,20 +2022,20 @@
       <c r="I7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="65" t="s">
+      <c r="J7" s="68" t="s">
         <v>45</v>
       </c>
       <c r="K7" s="24"/>
-      <c r="L7" s="65" t="s">
+      <c r="L7" s="68" t="s">
         <v>46</v>
       </c>
       <c r="M7" s="31"/>
     </row>
-    <row r="8" spans="1:13" ht="121.5">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
+    <row r="8" spans="1:13" ht="120">
+      <c r="A8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
       <c r="E8" s="25" t="s">
         <v>32</v>
       </c>
@@ -1923,16 +2049,16 @@
       <c r="I8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="65"/>
+      <c r="J8" s="68"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="65"/>
+      <c r="L8" s="68"/>
       <c r="M8" s="28"/>
     </row>
-    <row r="9" spans="1:13" ht="167.25">
-      <c r="A9" s="65"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
+    <row r="9" spans="1:13" ht="180">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
       <c r="E9" s="25" t="s">
         <v>64</v>
       </c>
@@ -1948,9 +2074,9 @@
       <c r="I9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="65"/>
+      <c r="J9" s="68"/>
       <c r="K9" s="24"/>
-      <c r="L9" s="65"/>
+      <c r="L9" s="68"/>
       <c r="M9" s="28"/>
     </row>
     <row r="10" spans="1:13">
@@ -2007,7 +2133,7 @@
     <col min="12" max="12" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.5">
+    <row r="1" spans="1:12" ht="45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2036,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L1" s="17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="57.95">
+    <row r="2" spans="1:12" ht="60">
       <c r="A2" s="2">
         <v>143659</v>
       </c>
@@ -2071,19 +2197,19 @@
         <v>28</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="57.95">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="60">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -2092,7 +2218,7 @@
         <v>29</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -2101,19 +2227,19 @@
         <v>4</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="57.95">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -2122,7 +2248,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -2134,22 +2260,22 @@
         <v>60</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="101.45">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="135">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="2"/>
       <c r="E5" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>62</v>
@@ -2161,19 +2287,19 @@
         <v>3</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="130.5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="150">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
@@ -2191,19 +2317,19 @@
         <v>30</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J6" s="13">
         <v>500</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="14.45">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
@@ -2216,7 +2342,7 @@
       <c r="J7" s="13"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="72.599999999999994">
+    <row r="8" spans="1:12" ht="90">
       <c r="A8" s="2">
         <v>5574</v>
       </c>
@@ -2224,7 +2350,7 @@
         <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2">
         <v>2170030</v>
@@ -2233,52 +2359,52 @@
         <v>19</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="72.599999999999994">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="75">
       <c r="E9" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>51</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J9" s="13"/>
       <c r="K9" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="130.5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="150">
       <c r="E10" s="4" t="s">
         <v>64</v>
       </c>
@@ -2292,23 +2418,23 @@
         <v>50</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="14.45"/>
-    <row r="12" spans="1:12" ht="14.45"/>
-    <row r="13" spans="1:12" ht="14.45">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12"/>
+    <row r="12" spans="1:12"/>
+    <row r="13" spans="1:12">
       <c r="A13" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2340,179 +2466,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="68" t="s">
+    <row r="2" spans="1:2" ht="45">
+      <c r="A2" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="57" t="s">
-        <v>98</v>
+      <c r="B2" s="41" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="68" t="s">
+      <c r="A3" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="45">
+      <c r="A4" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="57" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="68" t="s">
+      <c r="B4" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="57" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="64" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="68" t="s">
+      <c r="B5" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="57" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="90">
+      <c r="A6" s="64" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="68" t="s">
+      <c r="B6" s="41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45">
+      <c r="A7" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="68" t="s">
+      <c r="B7" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="57" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="45">
+      <c r="A8" s="64" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="68" t="s">
+      <c r="B8" s="41" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45">
+      <c r="A9" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="68" t="s">
+      <c r="B9" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="69" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="45">
+      <c r="A10" s="64" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="68" t="s">
+      <c r="B10" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="69" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="30">
+      <c r="A11" s="64" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="68" t="s">
+      <c r="B11" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="57" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="45">
+      <c r="A12" s="64" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="68" t="s">
+      <c r="B12" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="69" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="30">
+      <c r="A13" s="64" t="s">
         <v>116</v>
       </c>
+      <c r="B13" s="65" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="B14" s="69" t="s">
+      <c r="A14" s="64" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="68" t="s">
+      <c r="B14" s="65" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="69" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="30">
+      <c r="A15" s="64" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="68" t="s">
+      <c r="B15" s="65" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="69" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="30">
+      <c r="A16" s="64" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="68" t="s">
+      <c r="B16" s="65" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30">
+      <c r="A17" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="68" t="s">
+      <c r="B17" s="41" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30">
+      <c r="A18" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="69" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="68" t="s">
+      <c r="B18" s="65" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="69" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="75">
+      <c r="A19" s="64" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="68" t="s">
+      <c r="B19" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="69" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="30">
+      <c r="A20" s="64" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="68" t="s">
+      <c r="B20" s="65" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45">
+      <c r="A21" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="70" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="68" t="s">
+      <c r="B21" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="69" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="30">
+      <c r="A22" s="64" t="s">
         <v>131</v>
+      </c>
+      <c r="B22" s="65" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2574,15 +2700,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2837,14 +2954,55 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4264E7FE-F362-4EE6-893A-3F86363FF155}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4264E7FE-F362-4EE6-893A-3F86363FF155}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A49A9A2-FEBA-42A5-A8DD-B55DB902703E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDBC726A-7CEF-4FCE-950C-70EF97981F6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
+    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDBC726A-7CEF-4FCE-950C-70EF97981F6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A49A9A2-FEBA-42A5-A8DD-B55DB902703E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Uganda - Energy Projects.xlsx
@@ -143,7 +143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -341,23 +341,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -558,16 +547,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -576,10 +557,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,6 +632,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1370,15 +1377,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="83" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="83" t="n"/>
-      <c r="M7" s="84" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M7" s="55" t="n"/>
       <c r="N7" s="57" t="n"/>
       <c r="O7" s="37" t="n"/>
       <c r="P7" s="68" t="n"/>
@@ -1527,8 +1530,8 @@
       <c r="X9" s="47" t="n"/>
     </row>
     <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="94" t="n"/>
-      <c r="B10" s="94" t="n"/>
+      <c r="A10" s="38" t="n"/>
+      <c r="B10" s="38" t="n"/>
       <c r="C10" s="63" t="n"/>
       <c r="D10" s="57" t="n"/>
       <c r="E10" s="57" t="n"/>
@@ -1579,8 +1582,8 @@
       <c r="X10" s="77" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="95" t="n"/>
-      <c r="B11" s="95" t="n"/>
+      <c r="A11" s="38" t="n"/>
+      <c r="B11" s="38" t="n"/>
       <c r="C11" s="63" t="n"/>
       <c r="D11" s="57" t="n"/>
       <c r="E11" s="57" t="n"/>
@@ -1597,15 +1600,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="72" t="n">
+      <c r="K11" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="85" t="n"/>
-      <c r="M11" s="86" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="73" t="n"/>
       <c r="N11" s="62" t="n"/>
       <c r="O11" s="74" t="n"/>
       <c r="P11" s="75" t="n"/>
@@ -1619,13 +1618,19 @@
       <c r="X11" s="77" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="95" t="n"/>
-      <c r="B12" s="95" t="n"/>
+      <c r="A12" s="78" t="n">
+        <v>5711</v>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>Building Resilient Communities, Wetland Ecosystems and Associated Catchments in Uganda</t>
+        </is>
+      </c>
       <c r="C12" s="80" t="n"/>
       <c r="D12" s="80" t="n"/>
-      <c r="E12" s="87" t="n"/>
-      <c r="F12" s="87" t="n"/>
-      <c r="G12" s="87" t="n"/>
+      <c r="E12" s="85" t="n"/>
+      <c r="F12" s="85" t="n"/>
+      <c r="G12" s="85" t="n"/>
       <c r="H12" s="80" t="n"/>
       <c r="I12" s="80" t="n"/>
       <c r="J12" s="80" t="n"/>
@@ -1645,8 +1650,6 @@
       <c r="X12" s="2" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="95" t="n"/>
-      <c r="B13" s="95" t="n"/>
       <c r="C13" s="80" t="n"/>
       <c r="D13" s="80" t="n"/>
       <c r="E13" s="80" t="n"/>
@@ -1671,8 +1674,6 @@
       <c r="X13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="88" t="n"/>
-      <c r="B14" s="88" t="n"/>
       <c r="C14" s="80" t="n"/>
       <c r="D14" s="80" t="n"/>
       <c r="E14" s="80" t="n"/>
@@ -1697,8 +1698,6 @@
       <c r="X14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="89" t="n"/>
-      <c r="B15" s="89" t="n"/>
       <c r="C15" s="80" t="n"/>
       <c r="D15" s="80" t="n"/>
       <c r="E15" s="80" t="n"/>
@@ -1723,11 +1722,7 @@
       <c r="X15" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
-  </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1758,17 +1753,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1907,10 +1897,10 @@
       <c r="M2" s="31" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="90" t="n"/>
-      <c r="B3" s="90" t="n"/>
-      <c r="C3" s="90" t="n"/>
-      <c r="D3" s="90" t="n"/>
+      <c r="A3" s="86" t="n"/>
+      <c r="B3" s="86" t="n"/>
+      <c r="C3" s="86" t="n"/>
+      <c r="D3" s="86" t="n"/>
       <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Education Services</t>
@@ -1932,16 +1922,16 @@
           <t>3 Selected public schools will benefit from solar PV installations. Total estimated school popultation is 1500</t>
         </is>
       </c>
-      <c r="J3" s="90" t="n"/>
+      <c r="J3" s="86" t="n"/>
       <c r="K3" s="24" t="n"/>
-      <c r="L3" s="90" t="n"/>
+      <c r="L3" s="86" t="n"/>
       <c r="M3" s="31" t="n"/>
     </row>
     <row r="4" ht="75" customHeight="1">
-      <c r="A4" s="90" t="n"/>
-      <c r="B4" s="90" t="n"/>
-      <c r="C4" s="90" t="n"/>
-      <c r="D4" s="90" t="n"/>
+      <c r="A4" s="86" t="n"/>
+      <c r="B4" s="86" t="n"/>
+      <c r="C4" s="86" t="n"/>
+      <c r="D4" s="86" t="n"/>
       <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
@@ -1965,16 +1955,16 @@
           <t xml:space="preserve">The project will support schools to shift from using biomass to electricity for cooking. This will feature both on-grid and off-grid applications. </t>
         </is>
       </c>
-      <c r="J4" s="90" t="n"/>
+      <c r="J4" s="86" t="n"/>
       <c r="K4" s="24" t="n"/>
-      <c r="L4" s="90" t="n"/>
+      <c r="L4" s="86" t="n"/>
       <c r="M4" s="28" t="n"/>
     </row>
     <row r="5" ht="240" customHeight="1">
-      <c r="A5" s="90" t="n"/>
-      <c r="B5" s="90" t="n"/>
-      <c r="C5" s="90" t="n"/>
-      <c r="D5" s="90" t="n"/>
+      <c r="A5" s="86" t="n"/>
+      <c r="B5" s="86" t="n"/>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
       <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
@@ -1999,16 +1989,16 @@
 The project will support piloting use of solar power refrigeration/cooling in 3 urban markets to catalyze use of clean energy in local markets to reduce post-harvest food losses and increase revenue for small businesses which are mostly owned by women. </t>
         </is>
       </c>
-      <c r="J5" s="90" t="n"/>
+      <c r="J5" s="86" t="n"/>
       <c r="K5" s="24" t="n"/>
-      <c r="L5" s="90" t="n"/>
+      <c r="L5" s="86" t="n"/>
       <c r="M5" s="28" t="n"/>
     </row>
     <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="91" t="n"/>
-      <c r="B6" s="91" t="n"/>
-      <c r="C6" s="91" t="n"/>
-      <c r="D6" s="91" t="n"/>
+      <c r="A6" s="87" t="n"/>
+      <c r="B6" s="87" t="n"/>
+      <c r="C6" s="87" t="n"/>
+      <c r="D6" s="87" t="n"/>
       <c r="E6" s="26" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -2031,9 +2021,9 @@
 The project will facilitate training in operation and maintenance of solar PV installations for selected technicians in the project districts. </t>
         </is>
       </c>
-      <c r="J6" s="91" t="n"/>
+      <c r="J6" s="87" t="n"/>
       <c r="K6" s="24" t="n"/>
-      <c r="L6" s="91" t="n"/>
+      <c r="L6" s="87" t="n"/>
       <c r="M6" s="28" t="n"/>
     </row>
     <row r="7" ht="345" customHeight="1">
@@ -2090,10 +2080,10 @@
       <c r="M7" s="31" t="n"/>
     </row>
     <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="90" t="n"/>
-      <c r="B8" s="90" t="n"/>
-      <c r="C8" s="90" t="n"/>
-      <c r="D8" s="90" t="n"/>
+      <c r="A8" s="86" t="n"/>
+      <c r="B8" s="86" t="n"/>
+      <c r="C8" s="86" t="n"/>
+      <c r="D8" s="86" t="n"/>
       <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Electricity Access</t>
@@ -2114,16 +2104,16 @@
 Estimating 2kW per household and average household size of 5, the project can benefit 200 people</t>
         </is>
       </c>
-      <c r="J8" s="90" t="n"/>
+      <c r="J8" s="86" t="n"/>
       <c r="K8" s="24" t="n"/>
-      <c r="L8" s="90" t="n"/>
+      <c r="L8" s="86" t="n"/>
       <c r="M8" s="28" t="n"/>
     </row>
     <row r="9" ht="180" customHeight="1">
-      <c r="A9" s="91" t="n"/>
-      <c r="B9" s="91" t="n"/>
-      <c r="C9" s="91" t="n"/>
-      <c r="D9" s="91" t="n"/>
+      <c r="A9" s="87" t="n"/>
+      <c r="B9" s="87" t="n"/>
+      <c r="C9" s="87" t="n"/>
+      <c r="D9" s="87" t="n"/>
       <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -2147,9 +2137,9 @@
 Project will support training of technians on design, installation and operation and mainteannce of biogas system</t>
         </is>
       </c>
-      <c r="J9" s="91" t="n"/>
+      <c r="J9" s="87" t="n"/>
       <c r="K9" s="24" t="n"/>
-      <c r="L9" s="91" t="n"/>
+      <c r="L9" s="87" t="n"/>
       <c r="M9" s="28" t="n"/>
     </row>
     <row r="10">
@@ -2655,288 +2645,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="92" t="inlineStr">
+      <c r="A1" s="88" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="92" t="inlineStr">
+      <c r="B1" s="88" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="93" t="inlineStr">
+      <c r="A2" s="89" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="93" t="inlineStr">
+      <c r="B2" s="89" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="A3" s="89" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="93" t="inlineStr">
+      <c r="B3" s="89" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="93" t="inlineStr">
+      <c r="A4" s="89" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="93" t="inlineStr">
+      <c r="B4" s="89" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="93" t="inlineStr">
+      <c r="A5" s="89" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="89" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="93" t="inlineStr">
+      <c r="A6" s="89" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="93" t="inlineStr">
+      <c r="B6" s="89" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="89" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="93" t="inlineStr">
+      <c r="A8" s="89" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="93" t="inlineStr">
+      <c r="B8" s="89" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="89" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="89" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="93" t="inlineStr">
+      <c r="A10" s="89" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="93" t="inlineStr">
+      <c r="B10" s="89" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="89" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="89" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="93" t="inlineStr">
+      <c r="A12" s="89" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="93" t="inlineStr">
+      <c r="B12" s="89" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="93" t="inlineStr">
+      <c r="A13" s="89" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="89" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="93" t="inlineStr">
+      <c r="A14" s="89" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="93" t="inlineStr">
+      <c r="B14" s="89" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="93" t="inlineStr">
+      <c r="A15" s="89" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="89" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="93" t="inlineStr">
+      <c r="A16" s="89" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="93" t="inlineStr">
+      <c r="B16" s="89" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="93" t="inlineStr">
+      <c r="A17" s="89" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="89" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="93" t="inlineStr">
+      <c r="A18" s="89" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
+      <c r="B18" s="89" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="75" customHeight="1">
-      <c r="A19" s="93" t="inlineStr">
+      <c r="A19" s="89" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="93" t="inlineStr">
+      <c r="B19" s="89" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="93" t="inlineStr">
+      <c r="A20" s="89" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="93" t="inlineStr">
+      <c r="B20" s="89" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="93" t="inlineStr">
+      <c r="A21" s="89" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="89" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="93" t="inlineStr">
+      <c r="A22" s="89" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
+      <c r="B22" s="89" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="93" t="inlineStr">
+      <c r="A23" s="89" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="93" t="inlineStr">
+      <c r="B23" s="89" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="93" t="inlineStr">
+      <c r="A24" s="89" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="93" t="inlineStr">
+      <c r="B24" s="89" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
